--- a/research/traditional_assets/database/data/latvia/latvia_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/latvia/latvia_financial_svcs_non_bank_insurance.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0707</v>
+        <v>0.0907</v>
       </c>
       <c r="E2">
-        <v>0.302</v>
+        <v>0.182</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.00296875</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
+        <v>5.76</v>
+      </c>
+      <c r="L2">
+        <v>0.225</v>
+      </c>
+      <c r="M2">
+        <v>4.5</v>
+      </c>
+      <c r="N2">
+        <v>0.06267409470752089</v>
+      </c>
+      <c r="O2">
+        <v>0.78125</v>
+      </c>
+      <c r="P2">
+        <v>4.5</v>
+      </c>
+      <c r="Q2">
+        <v>0.06267409470752089</v>
+      </c>
+      <c r="R2">
+        <v>0.78125</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
         <v>3.93</v>
       </c>
-      <c r="L2">
-        <v>0.1665254237288135</v>
-      </c>
-      <c r="M2">
-        <v>4.88</v>
-      </c>
-      <c r="N2">
-        <v>0.06796657381615599</v>
-      </c>
-      <c r="O2">
-        <v>1.241730279898219</v>
-      </c>
-      <c r="P2">
-        <v>4.88</v>
-      </c>
-      <c r="Q2">
-        <v>0.06796657381615599</v>
-      </c>
-      <c r="R2">
-        <v>1.241730279898219</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>2.95</v>
-      </c>
       <c r="V2">
-        <v>0.04108635097493037</v>
+        <v>0.05473537604456825</v>
       </c>
       <c r="W2">
-        <v>0.3508928571428572</v>
+        <v>0.5702970297029702</v>
       </c>
       <c r="X2">
-        <v>0.03006613989806022</v>
+        <v>0.0586733706911922</v>
       </c>
       <c r="Y2">
-        <v>0.3208267172447969</v>
+        <v>0.5116236590117781</v>
       </c>
       <c r="Z2">
-        <v>0.5340574790676623</v>
+        <v>0.5181976438200884</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03114648415492823</v>
+        <v>0.05486016490776762</v>
       </c>
       <c r="AC2">
-        <v>-0.03114648415492823</v>
+        <v>-0.05486016490776762</v>
       </c>
       <c r="AD2">
-        <v>42.4</v>
+        <v>51.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>42.4</v>
+        <v>51.8</v>
       </c>
       <c r="AG2">
-        <v>39.45</v>
+        <v>47.87</v>
       </c>
       <c r="AH2">
-        <v>0.3712784588441331</v>
+        <v>0.4190938511326861</v>
       </c>
       <c r="AI2">
-        <v>0.8076190476190476</v>
+        <v>0.7551020408163266</v>
       </c>
       <c r="AJ2">
-        <v>0.3546067415730337</v>
+        <v>0.4000167126263893</v>
       </c>
       <c r="AK2">
-        <v>0.7961654894046417</v>
+        <v>0.7402195763104994</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0707</v>
+        <v>0.0907</v>
       </c>
       <c r="E3">
-        <v>0.302</v>
+        <v>0.182</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.00296875</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -728,85 +728,85 @@
         <v>0</v>
       </c>
       <c r="K3">
+        <v>5.76</v>
+      </c>
+      <c r="L3">
+        <v>0.225</v>
+      </c>
+      <c r="M3">
+        <v>4.5</v>
+      </c>
+      <c r="N3">
+        <v>0.06267409470752089</v>
+      </c>
+      <c r="O3">
+        <v>0.78125</v>
+      </c>
+      <c r="P3">
+        <v>4.5</v>
+      </c>
+      <c r="Q3">
+        <v>0.06267409470752089</v>
+      </c>
+      <c r="R3">
+        <v>0.78125</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
         <v>3.93</v>
       </c>
-      <c r="L3">
-        <v>0.1665254237288135</v>
-      </c>
-      <c r="M3">
-        <v>4.88</v>
-      </c>
-      <c r="N3">
-        <v>0.06796657381615599</v>
-      </c>
-      <c r="O3">
-        <v>1.241730279898219</v>
-      </c>
-      <c r="P3">
-        <v>4.88</v>
-      </c>
-      <c r="Q3">
-        <v>0.06796657381615599</v>
-      </c>
-      <c r="R3">
-        <v>1.241730279898219</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>2.95</v>
-      </c>
       <c r="V3">
-        <v>0.04108635097493037</v>
+        <v>0.05473537604456825</v>
       </c>
       <c r="W3">
-        <v>0.3508928571428572</v>
+        <v>0.5702970297029702</v>
       </c>
       <c r="X3">
-        <v>0.03006613989806022</v>
+        <v>0.0586733706911922</v>
       </c>
       <c r="Y3">
-        <v>0.3208267172447969</v>
+        <v>0.5116236590117781</v>
       </c>
       <c r="Z3">
-        <v>0.5340574790676623</v>
+        <v>0.5181976438200884</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.03114648415492823</v>
+        <v>0.05486016490776762</v>
       </c>
       <c r="AC3">
-        <v>-0.03114648415492823</v>
+        <v>-0.05486016490776762</v>
       </c>
       <c r="AD3">
-        <v>42.4</v>
+        <v>51.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>42.4</v>
+        <v>51.8</v>
       </c>
       <c r="AG3">
-        <v>39.45</v>
+        <v>47.87</v>
       </c>
       <c r="AH3">
-        <v>0.3712784588441331</v>
+        <v>0.4190938511326861</v>
       </c>
       <c r="AI3">
-        <v>0.8076190476190476</v>
+        <v>0.7551020408163266</v>
       </c>
       <c r="AJ3">
-        <v>0.3546067415730337</v>
+        <v>0.4000167126263893</v>
       </c>
       <c r="AK3">
-        <v>0.7961654894046417</v>
+        <v>0.7402195763104994</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/latvia/latvia_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/latvia/latvia_financial_svcs_non_bank_insurance.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0907</v>
+        <v>0.112</v>
       </c>
       <c r="E2">
-        <v>0.182</v>
+        <v>0.102</v>
       </c>
       <c r="G2">
-        <v>0.00296875</v>
+        <v>0.005079872204472843</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>5.76</v>
+        <v>7.43</v>
       </c>
       <c r="L2">
-        <v>0.225</v>
+        <v>0.2373801916932907</v>
       </c>
       <c r="M2">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="N2">
-        <v>0.06267409470752089</v>
+        <v>0.05428134556574923</v>
       </c>
       <c r="O2">
-        <v>0.78125</v>
+        <v>0.477792732166891</v>
       </c>
       <c r="P2">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q2">
-        <v>0.06267409470752089</v>
+        <v>0.05428134556574923</v>
       </c>
       <c r="R2">
-        <v>0.78125</v>
+        <v>0.477792732166891</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.93</v>
+        <v>3.41</v>
       </c>
       <c r="V2">
-        <v>0.05473537604456825</v>
+        <v>0.05214067278287462</v>
       </c>
       <c r="W2">
-        <v>0.5702970297029702</v>
+        <v>0.4422619047619047</v>
       </c>
       <c r="X2">
-        <v>0.0586733706911922</v>
+        <v>0.06864640576519077</v>
       </c>
       <c r="Y2">
-        <v>0.5116236590117781</v>
+        <v>0.373615498996714</v>
       </c>
       <c r="Z2">
-        <v>0.5181976438200884</v>
+        <v>0.4849405057015371</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05486016490776762</v>
+        <v>0.05654879569216523</v>
       </c>
       <c r="AC2">
-        <v>-0.05486016490776762</v>
+        <v>-0.05654879569216523</v>
       </c>
       <c r="AD2">
-        <v>51.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>51.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="AG2">
-        <v>47.87</v>
+        <v>75.19</v>
       </c>
       <c r="AH2">
-        <v>0.4190938511326861</v>
+        <v>0.5458333333333333</v>
       </c>
       <c r="AI2">
-        <v>0.7551020408163266</v>
+        <v>0.7797619047619048</v>
       </c>
       <c r="AJ2">
-        <v>0.4000167126263893</v>
+        <v>0.5348175545913649</v>
       </c>
       <c r="AK2">
-        <v>0.7402195763104994</v>
+        <v>0.7720505185337303</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0907</v>
+        <v>0.112</v>
       </c>
       <c r="E3">
-        <v>0.182</v>
+        <v>0.102</v>
       </c>
       <c r="G3">
-        <v>0.00296875</v>
+        <v>0.005079872204472843</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>5.76</v>
+        <v>7.43</v>
       </c>
       <c r="L3">
-        <v>0.225</v>
+        <v>0.2373801916932907</v>
       </c>
       <c r="M3">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="N3">
-        <v>0.06267409470752089</v>
+        <v>0.05428134556574923</v>
       </c>
       <c r="O3">
-        <v>0.78125</v>
+        <v>0.477792732166891</v>
       </c>
       <c r="P3">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q3">
-        <v>0.06267409470752089</v>
+        <v>0.05428134556574923</v>
       </c>
       <c r="R3">
-        <v>0.78125</v>
+        <v>0.477792732166891</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.93</v>
+        <v>3.41</v>
       </c>
       <c r="V3">
-        <v>0.05473537604456825</v>
+        <v>0.05214067278287462</v>
       </c>
       <c r="W3">
-        <v>0.5702970297029702</v>
+        <v>0.4422619047619047</v>
       </c>
       <c r="X3">
-        <v>0.0586733706911922</v>
+        <v>0.06864640576519077</v>
       </c>
       <c r="Y3">
-        <v>0.5116236590117781</v>
+        <v>0.373615498996714</v>
       </c>
       <c r="Z3">
-        <v>0.5181976438200884</v>
+        <v>0.4849405057015371</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05486016490776762</v>
+        <v>0.05654879569216523</v>
       </c>
       <c r="AC3">
-        <v>-0.05486016490776762</v>
+        <v>-0.05654879569216523</v>
       </c>
       <c r="AD3">
-        <v>51.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>51.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="AG3">
-        <v>47.87</v>
+        <v>75.19</v>
       </c>
       <c r="AH3">
-        <v>0.4190938511326861</v>
+        <v>0.5458333333333333</v>
       </c>
       <c r="AI3">
-        <v>0.7551020408163266</v>
+        <v>0.7797619047619048</v>
       </c>
       <c r="AJ3">
-        <v>0.4000167126263893</v>
+        <v>0.5348175545913649</v>
       </c>
       <c r="AK3">
-        <v>0.7402195763104994</v>
+        <v>0.7720505185337303</v>
       </c>
       <c r="AL3">
         <v>0</v>
